--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I466"/>
+  <dimension ref="A1:I469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15752,6 +15752,105 @@
         <v>271.84</v>
       </c>
       <c r="I466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:34+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="C467" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="D467" t="n">
+        <v>371.42</v>
+      </c>
+      <c r="E467" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="F467" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="G467" t="n">
+        <v>372.41</v>
+      </c>
+      <c r="H467" t="n">
+        <v>250.39</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="C468" t="n">
+        <v>384.18</v>
+      </c>
+      <c r="D468" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="E468" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="F468" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="G468" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="H468" t="n">
+        <v>250.39</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="C469" t="n">
+        <v>384.18</v>
+      </c>
+      <c r="D469" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="E469" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="F469" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="G469" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="H469" t="n">
+        <v>239.88</v>
+      </c>
+      <c r="I469" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15768,7 +15867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B551"/>
+  <dimension ref="A1:B556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21281,6 +21380,56 @@
       </c>
       <c r="B551" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -21449,28 +21598,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7445168351580558</v>
+        <v>0.7414141651422377</v>
       </c>
       <c r="J2" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K2" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3611645486439942</v>
+        <v>0.3616411689116278</v>
       </c>
       <c r="M2" t="n">
-        <v>6.129158161430833</v>
+        <v>6.106754210223905</v>
       </c>
       <c r="N2" t="n">
-        <v>64.11605069891156</v>
+        <v>63.76095751698207</v>
       </c>
       <c r="O2" t="n">
-        <v>8.007249883631181</v>
+        <v>7.985045868182729</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8954249758864</v>
+        <v>375.9266806048337</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21527,28 +21676,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.225738483765159</v>
+        <v>1.227924251586069</v>
       </c>
       <c r="J3" t="n">
+        <v>468</v>
+      </c>
+      <c r="K3" t="n">
         <v>465</v>
       </c>
-      <c r="K3" t="n">
-        <v>462</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6077986884217776</v>
+        <v>0.6112371620181284</v>
       </c>
       <c r="M3" t="n">
-        <v>6.140349976068299</v>
+        <v>6.113463486967531</v>
       </c>
       <c r="N3" t="n">
-        <v>62.63601476035399</v>
+        <v>62.25964137692118</v>
       </c>
       <c r="O3" t="n">
-        <v>7.914291804094287</v>
+        <v>7.890477892809863</v>
       </c>
       <c r="P3" t="n">
-        <v>349.2930735790218</v>
+        <v>349.270822294474</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21605,28 +21754,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.318010209515406</v>
+        <v>1.315827695597078</v>
       </c>
       <c r="J4" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K4" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6643202902594357</v>
+        <v>0.6659941164348461</v>
       </c>
       <c r="M4" t="n">
-        <v>5.674435385604812</v>
+        <v>5.647588450754128</v>
       </c>
       <c r="N4" t="n">
-        <v>56.22375000233025</v>
+        <v>55.88498504534991</v>
       </c>
       <c r="O4" t="n">
-        <v>7.498249795941066</v>
+        <v>7.475626063772178</v>
       </c>
       <c r="P4" t="n">
-        <v>338.2747215087592</v>
+        <v>338.2971480042878</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21683,28 +21832,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.292235852032789</v>
+        <v>1.289892618337707</v>
       </c>
       <c r="J5" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K5" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6187966776075877</v>
+        <v>0.6204970194365145</v>
       </c>
       <c r="M5" t="n">
-        <v>5.628684475770465</v>
+        <v>5.604917972879334</v>
       </c>
       <c r="N5" t="n">
-        <v>66.1845840193064</v>
+        <v>65.78713712818835</v>
       </c>
       <c r="O5" t="n">
-        <v>8.135390833838679</v>
+        <v>8.110927020272612</v>
       </c>
       <c r="P5" t="n">
-        <v>336.4104987485872</v>
+        <v>336.4344636718061</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21761,28 +21910,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.188648265402663</v>
+        <v>1.189687469382539</v>
       </c>
       <c r="J6" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K6" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6343460123775146</v>
+        <v>0.6373412486061965</v>
       </c>
       <c r="M6" t="n">
-        <v>5.377002531849868</v>
+        <v>5.347706211484226</v>
       </c>
       <c r="N6" t="n">
-        <v>52.3498973433983</v>
+        <v>52.01911316664717</v>
       </c>
       <c r="O6" t="n">
-        <v>7.23532289144018</v>
+        <v>7.212427688833156</v>
       </c>
       <c r="P6" t="n">
-        <v>337.8401575407615</v>
+        <v>337.8295361605449</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21839,28 +21988,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.155050167644589</v>
+        <v>1.156788971735026</v>
       </c>
       <c r="J7" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K7" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4722703451810182</v>
+        <v>0.4757710058342334</v>
       </c>
       <c r="M7" t="n">
-        <v>7.127213658100066</v>
+        <v>7.090882235196579</v>
       </c>
       <c r="N7" t="n">
-        <v>96.42817761368356</v>
+        <v>95.82712514997166</v>
       </c>
       <c r="O7" t="n">
-        <v>9.819785008526591</v>
+        <v>9.789133013192316</v>
       </c>
       <c r="P7" t="n">
-        <v>338.1699142713449</v>
+        <v>338.152205814285</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21917,28 +22066,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.784029772385005</v>
+        <v>3.694860961987341</v>
       </c>
       <c r="J8" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K8" t="n">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1192214630060865</v>
+        <v>0.1147539525493744</v>
       </c>
       <c r="M8" t="n">
-        <v>73.51495461840891</v>
+        <v>73.69750696463319</v>
       </c>
       <c r="N8" t="n">
-        <v>6942.942392834786</v>
+        <v>6944.394044264355</v>
       </c>
       <c r="O8" t="n">
-        <v>83.32432053629232</v>
+        <v>83.33303093170412</v>
       </c>
       <c r="P8" t="n">
-        <v>230.3043833383163</v>
+        <v>231.2052528440285</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21976,7 +22125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I466"/>
+  <dimension ref="A1:I469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43749,6 +43898,147 @@
         </is>
       </c>
     </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:34+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-41.067055254069516,172.10441115396858</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-41.066375023847364,172.104366157193</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-41.06568813775421,172.10437736455128</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-41.06501589250534,172.10426475180668</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-41.06435134676221,172.10408699701546</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-41.06368423471308,172.1039308780731</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-41.062846055627595,172.10522065448447</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-41.06705475329963,172.1044153871569</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-41.066374300512244,172.10437227173512</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-41.065688708078866,172.10437254352067</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-41.06501651846899,172.1042594604851</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-41.06434999747372,172.10409840264003</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-41.063681091030595,172.10395745173733</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-41.062846055627595,172.10522065448447</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-41.06705475329963,172.1044153871569</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-41.066374300512244,172.10437227173512</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-41.065688708078866,172.10437254352067</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-41.06501651846899,172.1042594604851</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-41.06434999747372,172.10409840264003</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-41.063681091030595,172.10395745173733</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-41.062831434606835,172.10534423191712</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I469"/>
+  <dimension ref="A1:I474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15851,6 +15851,171 @@
         <v>239.88</v>
       </c>
       <c r="I469" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="C470" t="n">
+        <v>384.18</v>
+      </c>
+      <c r="D470" t="n">
+        <v>371.83</v>
+      </c>
+      <c r="E470" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="F470" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="G470" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="H470" t="n">
+        <v>231.25</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="C471" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="D471" t="n">
+        <v>370.77</v>
+      </c>
+      <c r="E471" t="n">
+        <v>366</v>
+      </c>
+      <c r="F471" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="G471" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="H471" t="n">
+        <v>211.16</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="C472" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="D472" t="n">
+        <v>370.77</v>
+      </c>
+      <c r="E472" t="n">
+        <v>366</v>
+      </c>
+      <c r="F472" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="G472" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="H472" t="n">
+        <v>203.02</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>392.46</v>
+      </c>
+      <c r="C473" t="n">
+        <v>383.27</v>
+      </c>
+      <c r="D473" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="E473" t="n">
+        <v>366.08</v>
+      </c>
+      <c r="F473" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="G473" t="n">
+        <v>367.31</v>
+      </c>
+      <c r="H473" t="n">
+        <v>169.92</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>393.43</v>
+      </c>
+      <c r="C474" t="n">
+        <v>384.46</v>
+      </c>
+      <c r="D474" t="n">
+        <v>373.62</v>
+      </c>
+      <c r="E474" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="F474" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="G474" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="H474" t="n">
+        <v>169.92</v>
+      </c>
+      <c r="I474" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15867,7 +16032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B556"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21430,6 +21595,56 @@
       </c>
       <c r="B556" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -21598,28 +21813,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7414141651422377</v>
+        <v>0.7348198923284969</v>
       </c>
       <c r="J2" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3616411689116278</v>
+        <v>0.3611653318585352</v>
       </c>
       <c r="M2" t="n">
-        <v>6.106754210223905</v>
+        <v>6.077834432253399</v>
       </c>
       <c r="N2" t="n">
-        <v>63.76095751698207</v>
+        <v>63.25425429389621</v>
       </c>
       <c r="O2" t="n">
-        <v>7.985045868182729</v>
+        <v>7.953254320961716</v>
       </c>
       <c r="P2" t="n">
-        <v>375.9266806048337</v>
+        <v>375.9933359184056</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21676,28 +21891,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.227924251586069</v>
+        <v>1.229482174126348</v>
       </c>
       <c r="J3" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K3" t="n">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6112371620181284</v>
+        <v>0.6161609011834308</v>
       </c>
       <c r="M3" t="n">
-        <v>6.113463486967531</v>
+        <v>6.058217753750364</v>
       </c>
       <c r="N3" t="n">
-        <v>62.25964137692118</v>
+        <v>61.61437456447234</v>
       </c>
       <c r="O3" t="n">
-        <v>7.890477892809863</v>
+        <v>7.849482439274092</v>
       </c>
       <c r="P3" t="n">
-        <v>349.270822294474</v>
+        <v>349.2548955863166</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21754,28 +21969,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.315827695597078</v>
+        <v>1.312343691102501</v>
       </c>
       <c r="J4" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6659941164348461</v>
+        <v>0.6687063466807909</v>
       </c>
       <c r="M4" t="n">
-        <v>5.647588450754128</v>
+        <v>5.602855157166524</v>
       </c>
       <c r="N4" t="n">
-        <v>55.88498504534991</v>
+        <v>55.33883628140092</v>
       </c>
       <c r="O4" t="n">
-        <v>7.475626063772178</v>
+        <v>7.439007748443398</v>
       </c>
       <c r="P4" t="n">
-        <v>338.2971480042878</v>
+        <v>338.333065949467</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21832,28 +22047,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.289892618337707</v>
+        <v>1.282834639667366</v>
       </c>
       <c r="J5" t="n">
+        <v>473</v>
+      </c>
+      <c r="K5" t="n">
         <v>468</v>
       </c>
-      <c r="K5" t="n">
-        <v>463</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6204970194365145</v>
+        <v>0.6215663862523839</v>
       </c>
       <c r="M5" t="n">
-        <v>5.604917972879334</v>
+        <v>5.583062648637512</v>
       </c>
       <c r="N5" t="n">
-        <v>65.78713712818835</v>
+        <v>65.27856095626316</v>
       </c>
       <c r="O5" t="n">
-        <v>8.110927020272612</v>
+        <v>8.07951489609761</v>
       </c>
       <c r="P5" t="n">
-        <v>336.4344636718061</v>
+        <v>336.5069260617169</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21910,28 +22125,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.189687469382539</v>
+        <v>1.189026934174023</v>
       </c>
       <c r="J6" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6373412486061965</v>
+        <v>0.6412906514692056</v>
       </c>
       <c r="M6" t="n">
-        <v>5.347706211484226</v>
+        <v>5.301908337758514</v>
       </c>
       <c r="N6" t="n">
-        <v>52.01911316664717</v>
+        <v>51.47908897109888</v>
       </c>
       <c r="O6" t="n">
-        <v>7.212427688833156</v>
+        <v>7.174892958860005</v>
       </c>
       <c r="P6" t="n">
-        <v>337.8295361605449</v>
+        <v>337.836344772277</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21988,28 +22203,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.156788971735026</v>
+        <v>1.155213484112407</v>
       </c>
       <c r="J7" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K7" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4757710058342334</v>
+        <v>0.4795577129272977</v>
       </c>
       <c r="M7" t="n">
-        <v>7.090882235196579</v>
+        <v>7.033473001371598</v>
       </c>
       <c r="N7" t="n">
-        <v>95.82712514997166</v>
+        <v>94.85325872359955</v>
       </c>
       <c r="O7" t="n">
-        <v>9.789133013192316</v>
+        <v>9.739263767020562</v>
       </c>
       <c r="P7" t="n">
-        <v>338.152205814285</v>
+        <v>338.1683753682638</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22066,28 +22281,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.694860961987341</v>
+        <v>3.466793189224639</v>
       </c>
       <c r="J8" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K8" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1147539525493744</v>
+        <v>0.1015646132706994</v>
       </c>
       <c r="M8" t="n">
-        <v>73.69750696463319</v>
+        <v>74.57863119349629</v>
       </c>
       <c r="N8" t="n">
-        <v>6944.394044264355</v>
+        <v>7063.009858319077</v>
       </c>
       <c r="O8" t="n">
-        <v>83.33303093170412</v>
+        <v>84.04171498915927</v>
       </c>
       <c r="P8" t="n">
-        <v>231.2052528440285</v>
+        <v>233.518573399507</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22125,7 +22340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I469"/>
+  <dimension ref="A1:I474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44039,6 +44254,241 @@
         </is>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-41.06705475329963,172.1044153871569</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-41.066374300512244,172.10437227173512</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-41.065688708078866,172.10437254352067</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-41.06501651846899,172.1042594604851</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-41.06434999747372,172.10409840264003</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-41.063681091030595,172.10395745173733</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-41.06281942885465,172.105445704118</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:18:49+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-41.067051846049175,172.10443996316553</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-41.06637168537491,172.10439437815546</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-41.06568723358054,172.10438500764837</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-41.06501217844939,172.10429614697938</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-41.06434984446155,172.10409969606135</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-41.06368068763725,172.1039608616321</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-41.062791480006226,172.10568192373967</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-41.067051846049175,172.10443996316553</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-41.06637168537491,172.10439437815546</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-41.06568723358054,172.10438500764837</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-41.06501217844939,172.10429614697938</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-41.06434984446155,172.10409969606135</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-41.06368068763725,172.1039608616321</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-41.06278015564543,172.10577763437303</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-41.06705422470903,172.10441985552225</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-41.066373034675024,172.10438297218346</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-41.065688833272056,172.10437148524565</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-41.06501228973209,172.1042952063001</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-41.06434654774128,172.10412756341017</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-41.06367714055357,172.103990845188</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-41.06273410613212,172.10616682593664</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-41.06705557400574,172.1044084494316</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-41.06637469000042,172.10436897928938</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-41.06569119803049,172.10435149560567</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-41.06501565603014,172.10426675075038</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-41.06434717370136,172.10412227214158</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-41.06367399685717,172.10401741884678</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-41.06273410613212,172.10616682593664</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I474"/>
+  <dimension ref="A1:I475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16013,9 +16013,42 @@
         <v>365.05</v>
       </c>
       <c r="H474" t="n">
-        <v>169.92</v>
+        <v>182.37</v>
       </c>
       <c r="I474" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>395.44</v>
+      </c>
+      <c r="C475" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="D475" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="E475" t="n">
+        <v>366.35</v>
+      </c>
+      <c r="F475" t="n">
+        <v>365</v>
+      </c>
+      <c r="G475" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="H475" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="I475" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16032,7 +16065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B561"/>
+  <dimension ref="A1:B562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21645,6 +21678,16 @@
       </c>
       <c r="B561" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -21813,28 +21856,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7348198923284969</v>
+        <v>0.7346552596001535</v>
       </c>
       <c r="J2" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K2" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3611653318585352</v>
+        <v>0.3619138312676053</v>
       </c>
       <c r="M2" t="n">
-        <v>6.077834432253399</v>
+        <v>6.065895639443436</v>
       </c>
       <c r="N2" t="n">
-        <v>63.25425429389621</v>
+        <v>63.1212917204783</v>
       </c>
       <c r="O2" t="n">
-        <v>7.953254320961716</v>
+        <v>7.94489091935681</v>
       </c>
       <c r="P2" t="n">
-        <v>375.9933359184056</v>
+        <v>375.9950134942543</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21891,28 +21934,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.229482174126348</v>
+        <v>1.230324031176007</v>
       </c>
       <c r="J3" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K3" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6161609011834308</v>
+        <v>0.6173133899642156</v>
       </c>
       <c r="M3" t="n">
-        <v>6.058217753750364</v>
+        <v>6.050218412420638</v>
       </c>
       <c r="N3" t="n">
-        <v>61.61437456447234</v>
+        <v>61.49605446993561</v>
       </c>
       <c r="O3" t="n">
-        <v>7.849482439274092</v>
+        <v>7.841942008835287</v>
       </c>
       <c r="P3" t="n">
-        <v>349.2548955863166</v>
+        <v>349.2462248632945</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21969,28 +22012,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.312343691102501</v>
+        <v>1.311883896253832</v>
       </c>
       <c r="J4" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K4" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6687063466807909</v>
+        <v>0.6693569052956854</v>
       </c>
       <c r="M4" t="n">
-        <v>5.602855157166524</v>
+        <v>5.592923832159374</v>
       </c>
       <c r="N4" t="n">
-        <v>55.33883628140092</v>
+        <v>55.22403660049946</v>
       </c>
       <c r="O4" t="n">
-        <v>7.439007748443398</v>
+        <v>7.431287681182815</v>
       </c>
       <c r="P4" t="n">
-        <v>338.333065949467</v>
+        <v>338.3378456354845</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22047,28 +22090,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.282834639667366</v>
+        <v>1.281118837839708</v>
       </c>
       <c r="J5" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K5" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6215663862523839</v>
+        <v>0.6216222052071992</v>
       </c>
       <c r="M5" t="n">
-        <v>5.583062648637512</v>
+        <v>5.580575028417319</v>
       </c>
       <c r="N5" t="n">
-        <v>65.27856095626316</v>
+        <v>65.19109085199649</v>
       </c>
       <c r="O5" t="n">
-        <v>8.07951489609761</v>
+        <v>8.074100002600693</v>
       </c>
       <c r="P5" t="n">
-        <v>336.5069260617169</v>
+        <v>336.5246785698101</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22125,28 +22168,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.189026934174023</v>
+        <v>1.187264155562515</v>
       </c>
       <c r="J6" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K6" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6412906514692056</v>
+        <v>0.6412182141391271</v>
       </c>
       <c r="M6" t="n">
-        <v>5.301908337758514</v>
+        <v>5.302879189870001</v>
       </c>
       <c r="N6" t="n">
-        <v>51.47908897109888</v>
+        <v>51.42403371276464</v>
       </c>
       <c r="O6" t="n">
-        <v>7.174892958860005</v>
+        <v>7.171055271908357</v>
       </c>
       <c r="P6" t="n">
-        <v>337.836344772277</v>
+        <v>337.8545823602126</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22203,28 +22246,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.155213484112407</v>
+        <v>1.150504762838273</v>
       </c>
       <c r="J7" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K7" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4795577129272977</v>
+        <v>0.4774096117929351</v>
       </c>
       <c r="M7" t="n">
-        <v>7.033473001371598</v>
+        <v>7.050041741413154</v>
       </c>
       <c r="N7" t="n">
-        <v>94.85325872359955</v>
+        <v>95.04307631542893</v>
       </c>
       <c r="O7" t="n">
-        <v>9.739263767020562</v>
+        <v>9.7490038627251</v>
       </c>
       <c r="P7" t="n">
-        <v>338.1683753682638</v>
+        <v>338.2169365656321</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22281,28 +22324,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.466793189224639</v>
+        <v>3.410891820277039</v>
       </c>
       <c r="J8" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K8" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1015646132706994</v>
+        <v>0.0982404716688996</v>
       </c>
       <c r="M8" t="n">
-        <v>74.57863119349629</v>
+        <v>74.8255639800489</v>
       </c>
       <c r="N8" t="n">
-        <v>7063.009858319077</v>
+        <v>7105.339681207221</v>
       </c>
       <c r="O8" t="n">
-        <v>84.04171498915927</v>
+        <v>84.29317695523892</v>
       </c>
       <c r="P8" t="n">
-        <v>233.518573399507</v>
+        <v>234.0902853611818</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22340,7 +22383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I474"/>
+  <dimension ref="A1:I475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44480,10 +44523,57 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>-41.06273410613212,172.10616682593664</t>
+          <t>-41.06275142702545,172.1060204382343</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-41.067058369967484,172.10438481412885</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-41.06637548288678,172.10436227681043</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-41.065689779175855,172.1043634893898</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-41.06501266531115,172.1042920315075</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-41.06434236075768,172.10416295611512</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>-41.06366126899688,172.10412500686513</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>-41.062709592227264,172.1063740026233</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
